--- a/google_upload/ZeoN8n.xlsx
+++ b/google_upload/ZeoN8n.xlsx
@@ -5,8 +5,8 @@
   <sheets>
     <sheet name="FAQ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Shopee" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Web" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lazada" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Lazada" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Web" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5852,62 +5852,62 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="b">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
+      <c r="A2" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="n">
         <v>48812712426</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>Nước rửa chén Vitamin E Pano Hương chanh Sạch dầu mỡ khử mùi tanh dịu da tay Nhiều dung tích</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>Nước rửa chén</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="0" t="n">
         <v>12350</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="0" t="n">
         <v>13140</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="0" t="n">
         <v>0.06</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="0" t="inlineStr">
         <is>
           <t>BEST_SELLER_TOP_1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="0" t="inlineStr">
         <is>
           <t>Nước rửa chén Vitamin E Pano Hương chanh Sạch dầu mỡ khử mùi tanh dịu da tay Nhiều dung tích</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="0" t="inlineStr">
         <is>
           <t>ban chay; best seller; nước rửa chén; pano; vitamin e</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Nước-rửa-chén-Vitamin-E-Pano-Hương-chanh-Sạch-dầu-mỡ-khử-mùi-tanh-dịu-da-tay-Nhiều-dung-tích-i.20523065.48812712426</t>
         </is>
       </c>
-      <c r="N2" t="b">
+      <c r="N2" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O2" s="14" t="n">
@@ -5915,62 +5915,62 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="b">
-        <v>1</v>
-      </c>
-      <c r="B3" t="n">
+      <c r="A3" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B3" s="0" t="n">
         <v>52063408473</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>[GIÁ RẺ] Bột giặt Pano Hương cam chanh oải hương Sạch quần áo ít cặn lưu hương lâu Túi 300g 2.4kg 5.5kg</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>Bột giặt</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="0" t="n">
         <v>46350</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="0" t="n">
         <v>51500</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="0" t="inlineStr">
         <is>
           <t>BEST_SELLER_TOP_2</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="0" t="inlineStr">
         <is>
           <t>[GIÁ RẺ] Bột giặt Pano Hương cam chanh oải hương Sạch quần áo ít cặn lưu hương lâu Túi 300g 2.4kg 5.5kg</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="0" t="inlineStr">
         <is>
           <t>ban chay; best seller; bột giặt; cam chanh; pano</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/-GIÁ-RẺ-Bột-giặt-Pano-Hương-cam-chanh-oải-hương-Sạch-quần-áo-ít-cặn-lưu-hương-lâu-Túi-300g-2.4kg-5.5kg-i.20523065.52063408473</t>
         </is>
       </c>
-      <c r="N3" t="b">
+      <c r="N3" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O3" s="14" t="n">
@@ -5978,62 +5978,62 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="b">
-        <v>1</v>
-      </c>
-      <c r="B4" t="n">
+      <c r="A4" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B4" s="0" t="n">
         <v>40332260600</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>Bột giặt ZeO Nha Đam lưu hương kép 400g 720g hương nha đam the mát giặt tay giặt máy dịu nhẹ sạch vết bẩn</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>Bột giặt</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="0" t="n">
         <v>17550</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="0" t="n">
         <v>27000</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="0" t="n">
         <v>0.35</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="0" t="inlineStr">
         <is>
           <t>BEST_SELLER_TOP_3</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="0" t="inlineStr">
         <is>
           <t>Bột giặt ZeO Nha Đam lưu hương kép 400g 720g hương nha đam the mát giặt tay giặt máy dịu nhẹ sạch vết bẩn</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="0" t="inlineStr">
         <is>
           <t>ban chay; best seller; bột giặt; zeo</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Bột-giặt-ZeO-Nha-Đam-lưu-hương-kép-400g-720g-hương-nha-đam-the-mát-giặt-tay-giặt-máy-dịu-nhẹ-sạch-vết-bẩn-i.20523065.40332260600</t>
         </is>
       </c>
-      <c r="N4" t="b">
+      <c r="N4" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O4" s="14" t="n">
@@ -6041,62 +6041,62 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="b">
-        <v>1</v>
-      </c>
-      <c r="B5" t="n">
+      <c r="A5" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B5" s="0" t="n">
         <v>22487353728</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>Nước giặt Pano Hương táo dứa hoa nhài đào Làm sạch khử mùi lưu hương lâu Túi 3.5kg</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>Nước giặt</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="0" t="n">
         <v>95058</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="0" t="n">
         <v>202251</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="0" t="n">
         <v>0.53</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="0" t="inlineStr">
         <is>
           <t>BEST_SELLER_TOP_4</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="0" t="inlineStr">
         <is>
           <t>Nước giặt Pano Hương táo dứa hoa nhài đào Làm sạch khử mùi lưu hương lâu Túi 3.5kg</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="0" t="inlineStr">
         <is>
           <t>ban chay; best seller; nước giặt; pano</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Nước-giặt-Pano-Hương-táo-dứa-hoa-nhài-đào-Làm-sạch-khử-mùi-lưu-hương-lâu-Túi-3.5kg-i.20523065.22487353728</t>
         </is>
       </c>
-      <c r="N5" t="b">
+      <c r="N5" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O5" s="14" t="n">
@@ -6104,62 +6104,62 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="b">
-        <v>1</v>
-      </c>
-      <c r="B6" t="n">
+      <c r="A6" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B6" s="0" t="n">
         <v>24182154808</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>Nước tẩy toilet đậm đặc ZeO Hương trái cây Tẩy cặn vôi ố vàng khử mùi hôi Chai 650ml</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>Tẩy Toilet</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="0" t="n">
         <v>23000</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="0" t="n">
         <v>46000</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="0" t="inlineStr">
         <is>
           <t>BEST_SELLER_TOP_5</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="0" t="inlineStr">
         <is>
           <t>Nước tẩy toilet đậm đặc ZeO Hương trái cây Tẩy cặn vôi ố vàng khử mùi hôi Chai 650ml</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="0" t="inlineStr">
         <is>
           <t>ban chay; best seller; tẩy toilet; zeo</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Nước-tẩy-toilet-đậm-đặc-ZeO-Hương-trái-cây-Tẩy-cặn-vôi-ố-vàng-khử-mùi-hôi-Chai-650ml-i.20523065.24182154808</t>
         </is>
       </c>
-      <c r="N6" t="b">
+      <c r="N6" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O6" s="14" t="n">
@@ -6167,62 +6167,62 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="b">
-        <v>1</v>
-      </c>
-      <c r="B7" t="n">
+      <c r="A7" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B7" s="0" t="n">
         <v>21036221733</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>Nước tẩy quần áo trắng ZeO Javel chai 500ml 1000ml không hương liệu tẩy trắng mạnh diệt khuẩn quần áo bề mặt</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>Nước tẩy trắng Javen</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="0" t="n">
         <v>10400</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="0" t="n">
         <v>16000</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="0" t="n">
         <v>0.35</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="0" t="inlineStr">
         <is>
           <t>BEST_SELLER_TOP_6</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="0" t="inlineStr">
         <is>
           <t>Nước tẩy quần áo trắng ZeO Javel chai 500ml 1000ml không hương liệu tẩy trắng mạnh diệt khuẩn quần áo bề mặt</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="0" t="inlineStr">
         <is>
           <t>ban chay; best seller; javel; nước tẩy trắng javen; zeo</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Nước-tẩy-quần-áo-trắng-ZeO-Javel-chai-500ml-1000ml-không-hương-liệu-tẩy-trắng-mạnh-diệt-khuẩn-quần-áo-bề-mặt-i.20523065.21036221733</t>
         </is>
       </c>
-      <c r="N7" t="b">
+      <c r="N7" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O7" s="14" t="n">
@@ -6230,62 +6230,62 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="b">
-        <v>1</v>
-      </c>
-      <c r="B8" t="n">
+      <c r="A8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B8" s="0" t="n">
         <v>49463437973</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>Nước rửa chén Pano Hương chanh tự nhiên Sạch dầu mỡ khử mùi tanh dịu da tay 400g 800g 1.5kg</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>Nước rửa chén</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="0" t="n">
         <v>13000</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="0" t="n">
         <v>22800</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="0" t="n">
         <v>0.43</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="0" t="inlineStr">
         <is>
           <t>BEST_SELLER_TOP_7</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="0" t="inlineStr">
         <is>
           <t>Nước rửa chén Pano Hương chanh tự nhiên Sạch dầu mỡ khử mùi tanh dịu da tay 400g 800g 1.5kg</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="0" t="inlineStr">
         <is>
           <t>ban chay; best seller; nước rửa chén; pano</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M8" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Nước-rửa-chén-Pano-Hương-chanh-tự-nhiên-Sạch-dầu-mỡ-khử-mùi-tanh-dịu-da-tay-400g-800g-1.5kg-i.20523065.49463437973</t>
         </is>
       </c>
-      <c r="N8" t="b">
+      <c r="N8" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O8" s="14" t="n">
@@ -6293,62 +6293,62 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="b">
-        <v>1</v>
-      </c>
-      <c r="B9" t="n">
+      <c r="A9" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B9" s="0" t="n">
         <v>42401783886</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>[COMBO] 10 gói Nước xả vải Nano Clean ZeO Hương hoa trắng xạ hương Mềm vải giảm nhăn 10 gói x 20g</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="0" t="inlineStr">
         <is>
           <t>Nước xả vải</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="0" t="n">
         <v>17100</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="0" t="n">
         <v>18000</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="0" t="inlineStr">
         <is>
           <t>BEST_SELLER_TOP_8</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="0" t="inlineStr">
         <is>
           <t>[COMBO] 10 gói Nước xả vải Nano Clean ZeO Hương hoa trắng xạ hương Mềm vải giảm nhăn 10 gói x 20g</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="0" t="inlineStr">
         <is>
           <t>ban chay; best seller; nano clean; nước xả vải; zeo</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L9" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M9" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/-COMBO-10-gói-Nước-xả-vải-Nano-Clean-ZeO-Hương-hoa-trắng-xạ-hương-Mềm-vải-giảm-nhăn-10-gói-x-20g-i.20523065.42401783886</t>
         </is>
       </c>
-      <c r="N9" t="b">
+      <c r="N9" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O9" s="14" t="n">
@@ -6356,62 +6356,62 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="b">
-        <v>1</v>
-      </c>
-      <c r="B10" t="n">
+      <c r="A10" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B10" s="0" t="n">
         <v>17978063713</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>Nước giặt 2in1 Oplus Hương nước hoa Pháp Sạch quần áo mềm vải lưu hương cả ngày Can 1kg 3.5kg</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>Oplus</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>Nước giặt</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="0" t="n">
         <v>62100</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="0" t="n">
         <v>69000</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="0" t="inlineStr">
         <is>
           <t>BEST_SELLER_TOP_9</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="0" t="inlineStr">
         <is>
           <t>Nước giặt 2in1 Oplus Hương nước hoa Pháp Sạch quần áo mềm vải lưu hương cả ngày Can 1kg 3.5kg</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" s="0" t="inlineStr">
         <is>
           <t>2in1; ban chay; best seller; nước giặt; oplus</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" s="0" t="inlineStr">
         <is>
           <t>Oplus</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M10" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Nước-giặt-2in1-Oplus-Hương-nước-hoa-Pháp-Sạch-quần-áo-mềm-vải-lưu-hương-cả-ngày-Can-1kg-3.5kg-i.20523065.17978063713</t>
         </is>
       </c>
-      <c r="N10" t="b">
+      <c r="N10" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O10" s="14" t="n">
@@ -6419,62 +6419,62 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="b">
-        <v>1</v>
-      </c>
-      <c r="B11" t="n">
+      <c r="A11" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B11" s="0" t="n">
         <v>19119327902</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>[SIÊU TIẾT KIỆM] Nước lau sàn Pano Hương Hoa Hạ phấn em bé Sạch sàn khử mùi thơm lâu Chai Can 1kg 3.8kg</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>Nước lau sàn</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="0" t="n">
         <v>29450</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="0" t="n">
         <v>52500</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="0" t="n">
         <v>0.44</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="0" t="inlineStr">
         <is>
           <t>BEST_SELLER_TOP_10</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="0" t="inlineStr">
         <is>
           <t>[SIÊU TIẾT KIỆM] Nước lau sàn Pano Hương Hoa Hạ phấn em bé Sạch sàn khử mùi thơm lâu Chai Can 1kg 3.8kg</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="0" t="inlineStr">
         <is>
           <t>ban chay; best seller; nước lau sàn; pano</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L11" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M11" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/-SIÊU-TIẾT-KIỆM-Nước-lau-sàn-Pano-Hương-Hoa-Hạ-phấn-em-bé-Sạch-sàn-khử-mùi-thơm-lâu-Chai-Can-1kg-3.8kg-i.20523065.19119327902</t>
         </is>
       </c>
-      <c r="N11" t="b">
+      <c r="N11" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O11" s="14" t="n">
@@ -6482,62 +6482,62 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="b">
-        <v>1</v>
-      </c>
-      <c r="B12" t="n">
+      <c r="A12" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B12" s="0" t="n">
         <v>49011246861</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>[COMBO] 2 túi Nước giặt xả 2in1 Oplus Hương nước hoa Pháp Sạch sâu mềm vải thơm lâu 2 túi tổng 3.6kg</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>Oplus</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>Nước giặt</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="0" t="n">
         <v>133479</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="0" t="n">
         <v>290171</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="0" t="n">
         <v>0.54</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="0" t="inlineStr">
         <is>
           <t>NEW_ARRIVAL_TOP_1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="0" t="inlineStr">
         <is>
           <t>[COMBO] 2 túi Nước giặt xả 2in1 Oplus Hương nước hoa Pháp Sạch sâu mềm vải thơm lâu 2 túi tổng 3.6kg</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="0" t="inlineStr">
         <is>
           <t>2in1; moi nhat; moi ra; nước giặt; oplus</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" s="0" t="inlineStr">
         <is>
           <t>Oplus</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M12" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/-COMBO-2-túi-Nước-giặt-xả-2in1-Oplus-Hương-nước-hoa-Pháp-Sạch-sâu-mềm-vải-thơm-lâu-2-túi-tổng-3.6kg-i.20523065.49011246861</t>
         </is>
       </c>
-      <c r="N12" t="b">
+      <c r="N12" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O12" s="14" t="n">
@@ -6545,62 +6545,62 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="b">
-        <v>1</v>
-      </c>
-      <c r="B13" t="n">
+      <c r="A13" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B13" s="0" t="n">
         <v>44862653278</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>Bột giặt Oplus túi 720g 5.5kg hương hoa trắng xạ hương giặt tay giặt máy sạch vết bẩn làm mới quần áo sỉn màu</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>Oplus</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>Bột giặt</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="0" t="n">
         <v>66000</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="0" t="n">
         <v>110000</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="0" t="n">
         <v>0.4</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="0" t="inlineStr">
         <is>
           <t>NEW_ARRIVAL_TOP_4</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="0" t="inlineStr">
         <is>
           <t>Bột giặt Oplus túi 720g 5.5kg hương hoa trắng xạ hương giặt tay giặt máy sạch vết bẩn làm mới quần áo sỉn màu</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" s="0" t="inlineStr">
         <is>
           <t>bột giặt; moi nhat; moi ra; oplus</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L13" s="0" t="inlineStr">
         <is>
           <t>Oplus</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M13" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Bột-giặt-Oplus-túi-720g-5.5kg-hương-hoa-trắng-xạ-hương-giặt-tay-giặt-máy-sạch-vết-bẩn-làm-mới-quần-áo-sỉn-màu-i.20523065.44862653278</t>
         </is>
       </c>
-      <c r="N13" t="b">
+      <c r="N13" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O13" s="14" t="n">
@@ -6608,62 +6608,62 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="b">
-        <v>1</v>
-      </c>
-      <c r="B14" t="n">
+      <c r="A14" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B14" s="0" t="n">
         <v>40701777345</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>[MUA 1 TẶNG 1] Nước hoa treo xe ô tô Pano Hương nước hoa Pháp Khử mùi tỏa hương thư giãn [COMBO] 2 chai</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="0" t="inlineStr">
         <is>
           <t>Tẩy rửa &amp; Giặt giũ</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="0" t="n">
         <v>36000</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="0" t="n">
         <v>60000</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="0" t="n">
         <v>0.4</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="0" t="inlineStr">
         <is>
           <t>NEW_ARRIVAL_TOP_5</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="0" t="inlineStr">
         <is>
           <t>[MUA 1 TẶNG 1] Nước hoa treo xe ô tô Pano Hương nước hoa Pháp Khử mùi tỏa hương thư giãn [COMBO] 2 chai</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" s="0" t="inlineStr">
         <is>
           <t>moi nhat; moi ra; pano; treo xe; tẩy rửa &amp; giặt giũ</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L14" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M14" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/-MUA-1-TẶNG-1-Nước-hoa-treo-xe-ô-tô-Pano-Hương-nước-hoa-Pháp-Khử-mùi-tỏa-hương-thư-giãn-COMBO-2-chai-i.20523065.40701777345</t>
         </is>
       </c>
-      <c r="N14" t="b">
+      <c r="N14" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O14" s="14" t="n">
@@ -6671,62 +6671,62 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="b">
-        <v>1</v>
-      </c>
-      <c r="B15" t="n">
+      <c r="A15" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B15" s="0" t="n">
         <v>52863457457</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="0" t="inlineStr">
         <is>
           <t>Nước lau kính ZeO Hương trà xanh Sáng bóng khô nhanh không để lại vệt Chai 570ml</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="0" t="inlineStr">
         <is>
           <t>Nước lau kính</t>
         </is>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="0" t="n">
         <v>30100</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" s="0" t="n">
         <v>43000</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="0" t="inlineStr">
         <is>
           <t>NEW_ARRIVAL_TOP_6</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="0" t="inlineStr">
         <is>
           <t>Nước lau kính ZeO Hương trà xanh Sáng bóng khô nhanh không để lại vệt Chai 570ml</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" s="0" t="inlineStr">
         <is>
           <t>moi nhat; moi ra; nước lau kính; zeo</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L15" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M15" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Nước-lau-kính-ZeO-Hương-trà-xanh-Sáng-bóng-khô-nhanh-không-để-lại-vệt-Chai-570ml-i.20523065.52863457457</t>
         </is>
       </c>
-      <c r="N15" t="b">
+      <c r="N15" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O15" s="14" t="n">
@@ -6734,62 +6734,62 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="b">
-        <v>1</v>
-      </c>
-      <c r="B16" t="n">
+      <c r="A16" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B16" s="0" t="n">
         <v>57513424600</v>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
         <is>
           <t>[CAN TO TIẾT KIỆM] Nước giặt Pano Hương nước hoa Pháp Sạch sâu khử mùi lưu hương lâu Can 3.8kg</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="0" t="inlineStr">
         <is>
           <t>Nước giặt</t>
         </is>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="0" t="n">
         <v>123291</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="0" t="n">
         <v>205485</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" s="0" t="n">
         <v>0.4</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="0" t="inlineStr">
         <is>
           <t>NEW_ARRIVAL_TOP_7</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="0" t="inlineStr">
         <is>
           <t>[CAN TO TIẾT KIỆM] Nước giặt Pano Hương nước hoa Pháp Sạch sâu khử mùi lưu hương lâu Can 3.8kg</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" s="0" t="inlineStr">
         <is>
           <t>can 3.8kg; moi nhat; moi ra; nước giặt; pano</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L16" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M16" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/-CAN-TO-TIẾT-KIỆM-Nước-giặt-Pano-Hương-nước-hoa-Pháp-Sạch-sâu-khử-mùi-lưu-hương-lâu-Can-3.8kg-i.20523065.57513424600</t>
         </is>
       </c>
-      <c r="N16" t="b">
+      <c r="N16" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O16" s="14" t="n">
@@ -6797,62 +6797,62 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="b">
-        <v>1</v>
-      </c>
-      <c r="B17" t="n">
+      <c r="A17" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B17" s="0" t="n">
         <v>52213417021</v>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="0" t="inlineStr">
         <is>
           <t>[GÓI TIẾT KIỆM] Bột giặt Nha Đam ZeO Hương Fresh Floral Green Dịu nhẹ sạch vết bẩn lưu hương kép Túi 2.7kg 4.1kg</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="0" t="inlineStr">
         <is>
           <t>Bột giặt</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="0" t="n">
         <v>114855</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="0" t="n">
         <v>185250</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="0" t="n">
         <v>0.38</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="0" t="inlineStr">
         <is>
           <t>NEW_ARRIVAL_TOP_9</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="0" t="inlineStr">
         <is>
           <t>[GÓI TIẾT KIỆM] Bột giặt Nha Đam ZeO Hương Fresh Floral Green Dịu nhẹ sạch vết bẩn lưu hương kép Túi 2.7kg 4.1kg</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" s="0" t="inlineStr">
         <is>
           <t>bột giặt; fresh; moi nhat; moi ra; zeo</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L17" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M17" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/-GÓI-TIẾT-KIỆM-Bột-giặt-Nha-Đam-ZeO-Hương-Fresh-Floral-Green-Dịu-nhẹ-sạch-vết-bẩn-lưu-hương-kép-Túi-2.7kg-4.1kg-i.20523065.52213417021</t>
         </is>
       </c>
-      <c r="N17" t="b">
+      <c r="N17" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O17" s="14" t="n">
@@ -6860,62 +6860,62 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="b">
-        <v>1</v>
-      </c>
-      <c r="B18" t="n">
+      <c r="A18" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B18" s="0" t="n">
         <v>49063164373</v>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="0" t="inlineStr">
         <is>
           <t>[GIẶT NHANH] Nước giặt Bio Enzyme ZeO Hương tươi mát Đánh bay vết bẩn protein lưu hương Can 2kg 9kg</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="0" t="inlineStr">
         <is>
           <t>Nước giặt</t>
         </is>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="0" t="n">
         <v>104357</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="0" t="n">
         <v>168317</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="0" t="n">
         <v>0.38</v>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="0" t="inlineStr">
         <is>
           <t>NEW_ARRIVAL</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="0" t="inlineStr">
         <is>
           <t>[GIẶT NHANH] Nước giặt Bio Enzyme ZeO Hương tươi mát Đánh bay vết bẩn protein lưu hương Can 2kg 9kg</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" s="0" t="inlineStr">
         <is>
           <t>bio enzyme; moi nhat; moi ra; nước giặt; zeo</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L18" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M18" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/-GIẶT-NHANH-Nước-giặt-Bio-Enzyme-ZeO-Hương-tươi-mát-Đánh-bay-vết-bẩn-protein-lưu-hương-Can-2kg-9kg-i.20523065.49063164373</t>
         </is>
       </c>
-      <c r="N18" t="b">
+      <c r="N18" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O18" s="14" t="n">
@@ -6923,62 +6923,62 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="b">
-        <v>1</v>
-      </c>
-      <c r="B19" t="n">
+      <c r="A19" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B19" s="0" t="n">
         <v>44512305208</v>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr">
         <is>
           <t>[MỚI] Nước lau sàn Oplus Hương sả chanh Khử mùi sạch bóng sàn gỗ gạch men Can 1kg 3.6kg</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="0" t="inlineStr">
         <is>
           <t>Oplus</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="0" t="inlineStr">
         <is>
           <t>Nước lau sàn</t>
         </is>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="0" t="n">
         <v>34450</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="0" t="n">
         <v>53000</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="0" t="n">
         <v>0.35</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="0" t="inlineStr">
         <is>
           <t>NEW_ARRIVAL</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="0" t="inlineStr">
         <is>
           <t>[MỚI] Nước lau sàn Oplus Hương sả chanh Khử mùi sạch bóng sàn gỗ gạch men Can 1kg 3.6kg</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" s="0" t="inlineStr">
         <is>
           <t>moi nhat; moi ra; nước lau sàn; oplus</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L19" s="0" t="inlineStr">
         <is>
           <t>Oplus</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M19" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/-MỚI-Nước-lau-sàn-Oplus-Hương-sả-chanh-Khử-mùi-sạch-bóng-sàn-gỗ-gạch-men-Can-1kg-3.6kg-i.20523065.44512305208</t>
         </is>
       </c>
-      <c r="N19" t="b">
+      <c r="N19" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O19" s="14" t="n">
@@ -6986,62 +6986,62 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="b">
-        <v>1</v>
-      </c>
-      <c r="B20" t="n">
+      <c r="A20" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B20" s="0" t="n">
         <v>42923415834</v>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="0" t="inlineStr">
         <is>
           <t>Nước giặt Pano Active combo 2 túi 1.8kg tặng nước rửa chén 200g hương nước hoa Pháp giặt tay giặt máy sạch sâu</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="0" t="inlineStr">
         <is>
           <t>Nước giặt</t>
         </is>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="0" t="n">
         <v>147582</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="0" t="n">
         <v>238035</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="0" t="n">
         <v>0.38</v>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="0" t="inlineStr">
         <is>
           <t>NEW_ARRIVAL</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="0" t="inlineStr">
         <is>
           <t>Nước giặt Pano Active combo 2 túi 1.8kg tặng nước rửa chén 200g hương nước hoa Pháp giặt tay giặt máy sạch sâu</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" s="0" t="inlineStr">
         <is>
           <t>1.8kg; active; moi nhat; moi ra; nước giặt; pano</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L20" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M20" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Nước-giặt-Pano-Active-combo-2-túi-1.8kg-tặng-nước-rửa-chén-200g-hương-nước-hoa-Pháp-giặt-tay-giặt-máy-sạch-sâu-i.20523065.42923415834</t>
         </is>
       </c>
-      <c r="N20" t="b">
+      <c r="N20" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O20" s="14" t="n">
@@ -7049,62 +7049,62 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="b">
-        <v>1</v>
-      </c>
-      <c r="B21" t="n">
+      <c r="A21" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B21" s="0" t="n">
         <v>44123415679</v>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="0" t="inlineStr">
         <is>
           <t>Nước giặt Pano Fresh combo 2 gói 1 8kg tặng 1 nước rửa chén 200g hương hoa trắng giặt tay giặt máy sạch sâu vết bẩn</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="0" t="inlineStr">
         <is>
           <t>Nước giặt</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="0" t="n">
         <v>115795</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" s="0" t="n">
         <v>241239</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" s="0" t="n">
         <v>0.52</v>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="0" t="inlineStr">
         <is>
           <t>NEW_ARRIVAL</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="0" t="inlineStr">
         <is>
           <t>Nước giặt Pano Fresh combo 2 gói 1 8kg tặng 1 nước rửa chén 200g hương hoa trắng giặt tay giặt máy sạch sâu vết bẩn</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K21" s="0" t="inlineStr">
         <is>
           <t>fresh; moi nhat; moi ra; nước giặt; pano</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L21" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M21" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Nước-giặt-Pano-Fresh-combo-2-gói-1-8kg-tặng-1-nước-rửa-chén-200g-hương-hoa-trắng-giặt-tay-giặt-máy-sạch-sâu-vết-bẩn-i.20523065.44123415679</t>
         </is>
       </c>
-      <c r="N21" t="b">
+      <c r="N21" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O21" s="14" t="n">
@@ -7112,62 +7112,62 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="b">
-        <v>1</v>
-      </c>
-      <c r="B22" t="n">
+      <c r="A22" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B22" s="0" t="n">
         <v>27492729899</v>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t>Combo 2 túi Nước giặt Pano Warmish 1.8kg hương táo dứa hoa nhài sạch sâu vết bẩn tặng nước rửa chén 400g</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="0" t="inlineStr">
         <is>
           <t>Nước giặt</t>
         </is>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" s="0" t="n">
         <v>147582</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" s="0" t="n">
         <v>238035</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22" s="0" t="n">
         <v>0.38</v>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="0" t="inlineStr">
         <is>
           <t>NEW_ARRIVAL</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" s="0" t="inlineStr">
         <is>
           <t>Combo 2 túi Nước giặt Pano Warmish 1.8kg hương táo dứa hoa nhài sạch sâu vết bẩn tặng nước rửa chén 400g</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" s="0" t="inlineStr">
         <is>
           <t>1.8kg; moi nhat; moi ra; nước giặt; pano; warmish</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L22" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M22" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Combo-2-túi-Nước-giặt-Pano-Warmish-1.8kg-hương-táo-dứa-hoa-nhài-sạch-sâu-vết-bẩn-tặng-nước-rửa-chén-400g-i.20523065.27492729899</t>
         </is>
       </c>
-      <c r="N22" t="b">
+      <c r="N22" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O22" s="14" t="n">
@@ -7175,62 +7175,62 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="b">
-        <v>1</v>
-      </c>
-      <c r="B23" t="n">
+      <c r="A23" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B23" s="0" t="n">
         <v>40473414417</v>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>Nước giặt Pano Elegant 2 túi 1.8kg tặng nước rửa chén 200g hương nước hoa Pháp giặt tay giặt máy sạch sâu thơm lâu</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="0" t="inlineStr">
         <is>
           <t>Nước giặt</t>
         </is>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="0" t="n">
         <v>147582</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" s="0" t="n">
         <v>238035</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23" s="0" t="n">
         <v>0.38</v>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" s="0" t="inlineStr">
         <is>
           <t>NEW_ARRIVAL</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" s="0" t="inlineStr">
         <is>
           <t>Nước giặt Pano Elegant 2 túi 1.8kg tặng nước rửa chén 200g hương nước hoa Pháp giặt tay giặt máy sạch sâu thơm lâu</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K23" s="0" t="inlineStr">
         <is>
           <t>1.8kg; elegant; moi nhat; moi ra; nước giặt; pano</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L23" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M23" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Nước-giặt-Pano-Elegant-2-túi-1.8kg-tặng-nước-rửa-chén-200g-hương-nước-hoa-Pháp-giặt-tay-giặt-máy-sạch-sâu-thơm-lâu-i.20523065.40473414417</t>
         </is>
       </c>
-      <c r="N23" t="b">
+      <c r="N23" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O23" s="14" t="n">
@@ -7238,62 +7238,62 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="b">
-        <v>1</v>
-      </c>
-      <c r="B24" t="n">
+      <c r="A24" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B24" s="0" t="n">
         <v>56612838999</v>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
         <is>
           <t>Nước xả vải Nano Clean ZeO Hương hoa trắng xạ hương Mềm vải giảm nhăn thơm lâu Can 1kg 3.8kg</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="0" t="inlineStr">
         <is>
           <t>Nước xả vải</t>
         </is>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" s="0" t="n">
         <v>83200</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24" s="0" t="n">
         <v>128000</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24" s="0" t="n">
         <v>0.35</v>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="0" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" s="0" t="inlineStr">
         <is>
           <t>Nước xả vải Nano Clean ZeO Hương hoa trắng xạ hương Mềm vải giảm nhăn thơm lâu Can 1kg 3.8kg</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K24" s="0" t="inlineStr">
         <is>
           <t>nano clean; nước xả vải; zeo</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L24" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M24" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Nước-xả-vải-Nano-Clean-ZeO-Hương-hoa-trắng-xạ-hương-Mềm-vải-giảm-nhăn-thơm-lâu-Can-1kg-3.8kg-i.20523065.56612838999</t>
         </is>
       </c>
-      <c r="N24" t="b">
+      <c r="N24" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O24" s="14" t="n">
@@ -7301,62 +7301,62 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="b">
-        <v>1</v>
-      </c>
-      <c r="B25" t="n">
+      <c r="A25" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B25" s="0" t="n">
         <v>20119331885</v>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>Nước lau sàn ZeO Hương Ylang Ylang bạc hà Sạch bóng sàn khử mùi Can 1kg 3.8kg</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="0" t="inlineStr">
         <is>
           <t>Nước lau sàn</t>
         </is>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" s="0" t="n">
         <v>33150</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25" s="0" t="n">
         <v>44200</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25" s="0" t="n">
         <v>0.25</v>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" s="0" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" s="0" t="inlineStr">
         <is>
           <t>Nước lau sàn ZeO Hương Ylang Ylang bạc hà Sạch bóng sàn khử mùi Can 1kg 3.8kg</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K25" s="0" t="inlineStr">
         <is>
           <t>nước lau sàn; zeo</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L25" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M25" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Nước-lau-sàn-ZeO-Hương-Ylang-Ylang-bạc-hà-Sạch-bóng-sàn-khử-mùi-Can-1kg-3.8kg-i.20523065.20119331885</t>
         </is>
       </c>
-      <c r="N25" t="b">
+      <c r="N25" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O25" s="14" t="n">
@@ -7364,62 +7364,62 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="b">
-        <v>1</v>
-      </c>
-      <c r="B26" t="n">
+      <c r="A26" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B26" s="0" t="n">
         <v>17179798845</v>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="0" t="inlineStr">
         <is>
           <t>Chai xịt tẩy rửa đa năng Pano Hương trà xanh Đánh bay dầu mỡ vết bẩn đa bề mặt Chai 500ml</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="0" t="inlineStr">
         <is>
           <t>Tẩy rửa đa năng</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" s="0" t="n">
         <v>46620</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26" s="0" t="n">
         <v>74000</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26" s="0" t="n">
         <v>0.37</v>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="0" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J26" s="0" t="inlineStr">
         <is>
           <t>Chai xịt tẩy rửa đa năng Pano Hương trà xanh Đánh bay dầu mỡ vết bẩn đa bề mặt Chai 500ml</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" s="0" t="inlineStr">
         <is>
           <t>pano; tẩy rửa đa năng</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L26" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M26" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Chai-xịt-tẩy-rửa-đa-năng-Pano-Hương-trà-xanh-Đánh-bay-dầu-mỡ-vết-bẩn-đa-bề-mặt-Chai-500ml-i.20523065.17179798845</t>
         </is>
       </c>
-      <c r="N26" t="b">
+      <c r="N26" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O26" s="14" t="n">
@@ -7427,62 +7427,62 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="b">
-        <v>1</v>
-      </c>
-      <c r="B27" t="n">
+      <c r="A27" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B27" s="0" t="n">
         <v>18919306037</v>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="0" t="inlineStr">
         <is>
           <t>Nước rửa chén Enzyme ZeO Hương chanh tự nhiên Sạch dầu mỡ khử mùi tanh dịu da tay Can 400g 800g 1.5kg</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="0" t="inlineStr">
         <is>
           <t>Nước rửa chén</t>
         </is>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" s="0" t="n">
         <v>16900</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27" s="0" t="n">
         <v>26000</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27" s="0" t="n">
         <v>0.35</v>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" s="0" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" s="0" t="inlineStr">
         <is>
           <t>Nước rửa chén Enzyme ZeO Hương chanh tự nhiên Sạch dầu mỡ khử mùi tanh dịu da tay Can 400g 800g 1.5kg</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K27" s="0" t="inlineStr">
         <is>
           <t>nước rửa chén; zeo</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L27" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M27" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Nước-rửa-chén-Enzyme-ZeO-Hương-chanh-tự-nhiên-Sạch-dầu-mỡ-khử-mùi-tanh-dịu-da-tay-Can-400g-800g-1.5kg-i.20523065.18919306037</t>
         </is>
       </c>
-      <c r="N27" t="b">
+      <c r="N27" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O27" s="14" t="n">
@@ -7490,62 +7490,62 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="b">
-        <v>1</v>
-      </c>
-      <c r="B28" t="n">
+      <c r="A28" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B28" s="0" t="n">
         <v>19325680023</v>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="0" t="inlineStr">
         <is>
           <t>Nước giặt 2in1 Oplus Hương nước hoa Pháp Sạch vết bẩn mềm vải lưu hương kép Túi 2.4kg</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="0" t="inlineStr">
         <is>
           <t>Oplus</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="0" t="inlineStr">
         <is>
           <t>Nước giặt</t>
         </is>
       </c>
-      <c r="F28" t="n">
+      <c r="F28" s="0" t="n">
         <v>91257</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28" s="0" t="n">
         <v>172183</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28" s="0" t="n">
         <v>0.47</v>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" s="0" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28" s="0" t="inlineStr">
         <is>
           <t>Nước giặt 2in1 Oplus Hương nước hoa Pháp Sạch vết bẩn mềm vải lưu hương kép Túi 2.4kg</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K28" s="0" t="inlineStr">
         <is>
           <t>2in1; nước giặt; oplus</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L28" s="0" t="inlineStr">
         <is>
           <t>Oplus</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M28" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Nước-giặt-2in1-Oplus-Hương-nước-hoa-Pháp-Sạch-vết-bẩn-mềm-vải-lưu-hương-kép-Túi-2.4kg-i.20523065.19325680023</t>
         </is>
       </c>
-      <c r="N28" t="b">
+      <c r="N28" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O28" s="14" t="n">
@@ -7553,62 +7553,62 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="b">
-        <v>1</v>
-      </c>
-      <c r="B29" t="n">
+      <c r="A29" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B29" s="0" t="n">
         <v>19419299602</v>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="0" t="inlineStr">
         <is>
           <t>Nước giặt Pano Hương nước hoa Pháp Sạch vết bẩn khử mùi lưu hương lâu Can 3.6kg</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="0" t="inlineStr">
         <is>
           <t>Nước giặt</t>
         </is>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" s="0" t="n">
         <v>131100</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29" s="0" t="n">
         <v>234107</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29" s="0" t="n">
         <v>0.44</v>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" s="0" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J29" s="0" t="inlineStr">
         <is>
           <t>Nước giặt Pano Hương nước hoa Pháp Sạch vết bẩn khử mùi lưu hương lâu Can 3.6kg</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K29" s="0" t="inlineStr">
         <is>
           <t>can 3.6kg; nước giặt; pano</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L29" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M29" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Nước-giặt-Pano-Hương-nước-hoa-Pháp-Sạch-vết-bẩn-khử-mùi-lưu-hương-lâu-Can-3.6kg-i.20523065.19419299602</t>
         </is>
       </c>
-      <c r="N29" t="b">
+      <c r="N29" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O29" s="14" t="n">
@@ -7616,62 +7616,62 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="b">
-        <v>1</v>
-      </c>
-      <c r="B30" t="n">
+      <c r="A30" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B30" s="0" t="n">
         <v>55813079469</v>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="0" t="inlineStr">
         <is>
           <t>Bột giặt ZeO Bọt Biển Hương táo dứa hoa nhài Sạch vết bẩn lưu hương kép Túi 720g 2.7kg</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="0" t="inlineStr">
         <is>
           <t>Bột giặt</t>
         </is>
       </c>
-      <c r="F30" t="n">
+      <c r="F30" s="0" t="n">
         <v>35100</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30" s="0" t="n">
         <v>54000</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30" s="0" t="n">
         <v>0.35</v>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" s="0" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J30" s="0" t="inlineStr">
         <is>
           <t>Bột giặt ZeO Bọt Biển Hương táo dứa hoa nhài Sạch vết bẩn lưu hương kép Túi 720g 2.7kg</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K30" s="0" t="inlineStr">
         <is>
           <t>bột giặt; zeo</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L30" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M30" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Bột-giặt-ZeO-Bọt-Biển-Hương-táo-dứa-hoa-nhài-Sạch-vết-bẩn-lưu-hương-kép-Túi-720g-2.7kg-i.20523065.55813079469</t>
         </is>
       </c>
-      <c r="N30" t="b">
+      <c r="N30" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O30" s="14" t="n">
@@ -7679,62 +7679,62 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="b">
-        <v>1</v>
-      </c>
-      <c r="B31" t="n">
+      <c r="A31" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B31" s="0" t="n">
         <v>43251767103</v>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="0" t="inlineStr">
         <is>
           <t>Nước rửa chén Oplus Hương chanh tự nhiên Sạch dầu mỡ khử mùi tanh dịu da tay Bao bì nhiều lựa chọn</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="0" t="inlineStr">
         <is>
           <t>Oplus</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="0" t="inlineStr">
         <is>
           <t>Nước rửa chén</t>
         </is>
       </c>
-      <c r="F31" t="n">
+      <c r="F31" s="0" t="n">
         <v>14300</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31" s="0" t="n">
         <v>22000</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31" s="0" t="n">
         <v>0.35</v>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" s="0" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" s="0" t="inlineStr">
         <is>
           <t>Nước rửa chén Oplus Hương chanh tự nhiên Sạch dầu mỡ khử mùi tanh dịu da tay Bao bì nhiều lựa chọn</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" s="0" t="inlineStr">
         <is>
           <t>nước rửa chén; oplus</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L31" s="0" t="inlineStr">
         <is>
           <t>Oplus</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M31" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Nước-rửa-chén-Oplus-Hương-chanh-tự-nhiên-Sạch-dầu-mỡ-khử-mùi-tanh-dịu-da-tay-Bao-bì-nhiều-lựa-chọn-i.20523065.43251767103</t>
         </is>
       </c>
-      <c r="N31" t="b">
+      <c r="N31" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O31" s="14" t="n">
@@ -7742,62 +7742,62 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="b">
-        <v>1</v>
-      </c>
-      <c r="B32" t="n">
+      <c r="A32" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B32" s="0" t="n">
         <v>44472616843</v>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="0" t="inlineStr">
         <is>
           <t>Combo 2 nước giặt Pano 1.8kg hương nước hoa Pháp giặt tay giặt máy sạch sâu vết bẩn an toàn da tay</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="0" t="inlineStr">
         <is>
           <t>Nước giặt</t>
         </is>
       </c>
-      <c r="F32" t="n">
+      <c r="F32" s="0" t="n">
         <v>122550</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G32" s="0" t="n">
         <v>129000</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" s="0" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" s="0" t="inlineStr">
         <is>
           <t>Combo 2 nước giặt Pano 1.8kg hương nước hoa Pháp giặt tay giặt máy sạch sâu vết bẩn an toàn da tay</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" s="0" t="inlineStr">
         <is>
           <t>1.8kg; nước giặt; pano</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L32" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M32" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Combo-2-nước-giặt-Pano-1.8kg-hương-nước-hoa-Pháp-giặt-tay-giặt-máy-sạch-sâu-vết-bẩn-an-toàn-da-tay-i.20523065.44472616843</t>
         </is>
       </c>
-      <c r="N32" t="b">
+      <c r="N32" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O32" s="14" t="n">
@@ -7805,62 +7805,62 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="b">
-        <v>1</v>
-      </c>
-      <c r="B33" t="n">
+      <c r="A33" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B33" s="0" t="n">
         <v>24281041930</v>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="0" t="inlineStr">
         <is>
           <t>[TẶNG KÈM] 3 gói nước xả vải Bột giặt Oplus Hương hoa trắng xạ hương Tiết kiệm nước sạch vết bẩn ít cặn Túi 2kg</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="0" t="inlineStr">
         <is>
           <t>Oplus</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="0" t="inlineStr">
         <is>
           <t>Tẩy rửa &amp; Giặt giũ</t>
         </is>
       </c>
-      <c r="F33" t="n">
+      <c r="F33" s="0" t="n">
         <v>72150</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G33" s="0" t="n">
         <v>111000</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H33" s="0" t="n">
         <v>0.35</v>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" s="0" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" s="0" t="inlineStr">
         <is>
           <t>[TẶNG KÈM] 3 gói nước xả vải Bột giặt Oplus Hương hoa trắng xạ hương Tiết kiệm nước sạch vết bẩn ít cặn Túi 2kg</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K33" s="0" t="inlineStr">
         <is>
           <t>oplus; tẩy rửa &amp; giặt giũ</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L33" s="0" t="inlineStr">
         <is>
           <t>Oplus</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M33" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/-TẶNG-KÈM-3-gói-nước-xả-vải-Bột-giặt-Oplus-Hương-hoa-trắng-xạ-hương-Tiết-kiệm-nước-sạch-vết-bẩn-ít-cặn-Túi-2kg-i.20523065.24281041930</t>
         </is>
       </c>
-      <c r="N33" t="b">
+      <c r="N33" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O33" s="14" t="n">
@@ -7868,62 +7868,62 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="b">
-        <v>1</v>
-      </c>
-      <c r="B34" t="n">
+      <c r="A34" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B34" s="0" t="n">
         <v>20819334417</v>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="0" t="inlineStr">
         <is>
           <t>Nước giặt 2in1 Oplus Hương nước hoa Pháp Sạch sâu mềm vải không cần nước xả Can 1kg</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="0" t="inlineStr">
         <is>
           <t>Oplus</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="0" t="inlineStr">
         <is>
           <t>Nước giặt</t>
         </is>
       </c>
-      <c r="F34" t="n">
+      <c r="F34" s="0" t="n">
         <v>60720</v>
       </c>
-      <c r="G34" t="n">
+      <c r="G34" s="0" t="n">
         <v>69000</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H34" s="0" t="n">
         <v>0.12</v>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" s="0" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" s="0" t="inlineStr">
         <is>
           <t>Nước giặt 2in1 Oplus Hương nước hoa Pháp Sạch sâu mềm vải không cần nước xả Can 1kg</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K34" s="0" t="inlineStr">
         <is>
           <t>2in1; nước giặt; oplus</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L34" s="0" t="inlineStr">
         <is>
           <t>Oplus</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M34" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Nước-giặt-2in1-Oplus-Hương-nước-hoa-Pháp-Sạch-sâu-mềm-vải-không-cần-nước-xả-Can-1kg-i.20523065.20819334417</t>
         </is>
       </c>
-      <c r="N34" t="b">
+      <c r="N34" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O34" s="14" t="n">
@@ -7931,62 +7931,62 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="b">
-        <v>1</v>
-      </c>
-      <c r="B35" t="n">
+      <c r="A35" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B35" s="0" t="n">
         <v>55861226781</v>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="0" t="inlineStr">
         <is>
           <t>Nước giặt xả 2in1 Oplus Hương nước hoa Pháp Sạch sâu mềm vải không cần nước xả Túi 1.8kg</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="0" t="inlineStr">
         <is>
           <t>Oplus</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="0" t="inlineStr">
         <is>
           <t>Nước giặt</t>
         </is>
       </c>
-      <c r="F35" t="n">
+      <c r="F35" s="0" t="n">
         <v>77727</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G35" s="0" t="n">
         <v>119580</v>
       </c>
-      <c r="H35" t="n">
+      <c r="H35" s="0" t="n">
         <v>0.35</v>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" s="0" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" s="0" t="inlineStr">
         <is>
           <t>Nước giặt xả 2in1 Oplus Hương nước hoa Pháp Sạch sâu mềm vải không cần nước xả Túi 1.8kg</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K35" s="0" t="inlineStr">
         <is>
           <t>1.8kg; 2in1; nước giặt; oplus</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L35" s="0" t="inlineStr">
         <is>
           <t>Oplus</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M35" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Nước-giặt-xả-2in1-Oplus-Hương-nước-hoa-Pháp-Sạch-sâu-mềm-vải-không-cần-nước-xả-Túi-1.8kg-i.20523065.55861226781</t>
         </is>
       </c>
-      <c r="N35" t="b">
+      <c r="N35" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O35" s="14" t="n">
@@ -7994,62 +7994,62 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="b">
-        <v>1</v>
-      </c>
-      <c r="B36" t="n">
+      <c r="A36" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B36" s="0" t="n">
         <v>54212683981</v>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="0" t="inlineStr">
         <is>
           <t>Nước rửa chén Pano can 3.8kg hương chanh tự nhiên cho nhà hàng quán ăn sạch dầu mỡ khử mùi tanh da tay</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="0" t="inlineStr">
         <is>
           <t>Nước rửa chén</t>
         </is>
       </c>
-      <c r="F36" t="n">
+      <c r="F36" s="0" t="n">
         <v>76050</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G36" s="0" t="n">
         <v>117000</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H36" s="0" t="n">
         <v>0.35</v>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" s="0" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J36" s="0" t="inlineStr">
         <is>
           <t>Nước rửa chén Pano can 3.8kg hương chanh tự nhiên cho nhà hàng quán ăn sạch dầu mỡ khử mùi tanh da tay</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K36" s="0" t="inlineStr">
         <is>
           <t>can 3.8kg; nước rửa chén; pano</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="L36" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M36" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Nước-rửa-chén-Pano-can-3.8kg-hương-chanh-tự-nhiên-cho-nhà-hàng-quán-ăn-sạch-dầu-mỡ-khử-mùi-tanh-da-tay-i.20523065.54212683981</t>
         </is>
       </c>
-      <c r="N36" t="b">
+      <c r="N36" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O36" s="14" t="n">
@@ -8057,62 +8057,62 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="b">
-        <v>1</v>
-      </c>
-      <c r="B37" t="n">
+      <c r="A37" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B37" s="0" t="n">
         <v>21319337822</v>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="0" t="inlineStr">
         <is>
           <t>Bột giặt Nước hoa ZeO Hương hoa trắng xạ hương Sạch vết bẩn cứng đầu lưu hương kép Gói 720g 750g</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="0" t="inlineStr">
         <is>
           <t>Bột giặt</t>
         </is>
       </c>
-      <c r="F37" t="n">
+      <c r="F37" s="0" t="n">
         <v>36400</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G37" s="0" t="n">
         <v>45500</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H37" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I37" s="0" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" s="0" t="inlineStr">
         <is>
           <t>Bột giặt Nước hoa ZeO Hương hoa trắng xạ hương Sạch vết bẩn cứng đầu lưu hương kép Gói 720g 750g</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K37" s="0" t="inlineStr">
         <is>
           <t>bột giặt; zeo</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L37" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M37" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Bột-giặt-Nước-hoa-ZeO-Hương-hoa-trắng-xạ-hương-Sạch-vết-bẩn-cứng-đầu-lưu-hương-kép-Gói-720g-750g-i.20523065.21319337822</t>
         </is>
       </c>
-      <c r="N37" t="b">
+      <c r="N37" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O37" s="14" t="n">
@@ -8120,62 +8120,62 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="b">
-        <v>1</v>
-      </c>
-      <c r="B38" t="n">
+      <c r="A38" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B38" s="0" t="n">
         <v>28006686405</v>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="0" t="inlineStr">
         <is>
           <t>[SẠCH SÂU - TIẾT KIỆM] Nước giặt xả 2in1 Oplus Hương nước hoa Pháp Mềm vải lưu hương lâu Can 3.1kg 3.5kg</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="0" t="inlineStr">
         <is>
           <t>Oplus</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="0" t="inlineStr">
         <is>
           <t>Nước giặt</t>
         </is>
       </c>
-      <c r="F38" t="n">
+      <c r="F38" s="0" t="n">
         <v>129390</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G38" s="0" t="n">
         <v>227000</v>
       </c>
-      <c r="H38" t="n">
+      <c r="H38" s="0" t="n">
         <v>0.43</v>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I38" s="0" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" s="0" t="inlineStr">
         <is>
           <t>[SẠCH SÂU - TIẾT KIỆM] Nước giặt xả 2in1 Oplus Hương nước hoa Pháp Mềm vải lưu hương lâu Can 3.1kg 3.5kg</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K38" s="0" t="inlineStr">
         <is>
           <t>2in1; nước giặt; oplus</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L38" s="0" t="inlineStr">
         <is>
           <t>Oplus</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M38" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/-SẠCH-SÂU-TIẾT-KIỆM-Nước-giặt-xả-2in1-Oplus-Hương-nước-hoa-Pháp-Mềm-vải-lưu-hương-lâu-Can-3.1kg-3.5kg-i.20523065.28006686405</t>
         </is>
       </c>
-      <c r="N38" t="b">
+      <c r="N38" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O38" s="14" t="n">
@@ -8183,62 +8183,62 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="b">
-        <v>1</v>
-      </c>
-      <c r="B39" t="n">
+      <c r="A39" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B39" s="0" t="n">
         <v>40823425194</v>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="0" t="inlineStr">
         <is>
           <t>Nước giặt Pano combo 2 gói 1 8kg tặng nước rửa chén 400g hương hoa tươi mát giặt tay giặt máy sạch sâu vết bẩn</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="0" t="inlineStr">
         <is>
           <t>Nước giặt</t>
         </is>
       </c>
-      <c r="F39" t="n">
+      <c r="F39" s="0" t="n">
         <v>120640</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G39" s="0" t="n">
         <v>251333</v>
       </c>
-      <c r="H39" t="n">
+      <c r="H39" s="0" t="n">
         <v>0.52</v>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" s="0" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J39" s="0" t="inlineStr">
         <is>
           <t>Nước giặt Pano combo 2 gói 1 8kg tặng nước rửa chén 400g hương hoa tươi mát giặt tay giặt máy sạch sâu vết bẩn</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K39" s="0" t="inlineStr">
         <is>
           <t>nước giặt; pano</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L39" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M39" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Nước-giặt-Pano-combo-2-gói-1-8kg-tặng-nước-rửa-chén-400g-hương-hoa-tươi-mát-giặt-tay-giặt-máy-sạch-sâu-vết-bẩn-i.20523065.40823425194</t>
         </is>
       </c>
-      <c r="N39" t="b">
+      <c r="N39" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O39" s="14" t="n">
@@ -8246,62 +8246,62 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="b">
-        <v>1</v>
-      </c>
-      <c r="B40" t="n">
+      <c r="A40" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B40" s="0" t="n">
         <v>14789198137</v>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="0" t="inlineStr">
         <is>
           <t>Nước giặt ZeO Matic 3in1 2.2kg hương táo xạ hương gỗ cho máy giặt cửa trước cửa trên sạch khuẩn khử mùi</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="0" t="inlineStr">
         <is>
           <t>Nước giặt</t>
         </is>
       </c>
-      <c r="F40" t="n">
+      <c r="F40" s="0" t="n">
         <v>89000</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G40" s="0" t="n">
         <v>175000</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H40" s="0" t="n">
         <v>0.49</v>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I40" s="0" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J40" s="0" t="inlineStr">
         <is>
           <t>Nước giặt ZeO Matic 3in1 2.2kg hương táo xạ hương gỗ cho máy giặt cửa trước cửa trên sạch khuẩn khử mùi</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K40" s="0" t="inlineStr">
         <is>
           <t>nước giặt; zeo</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="L40" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="M40" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Nước-giặt-ZeO-Matic-3in1-2.2kg-hương-táo-xạ-hương-gỗ-cho-máy-giặt-cửa-trước-cửa-trên-sạch-khuẩn-khử-mùi-i.20523065.14789198137</t>
         </is>
       </c>
-      <c r="N40" t="b">
+      <c r="N40" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O40" s="14" t="n">
@@ -8309,62 +8309,62 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="b">
-        <v>1</v>
-      </c>
-      <c r="B41" t="n">
+      <c r="A41" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B41" s="0" t="n">
         <v>53011222501</v>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="0" t="inlineStr">
         <is>
           <t>[COMBO] 4 túi Nước giặt xả 2in1 Oplus Hương nước hoa Pháp Sạch sâu mềm vải thơm lâu 4 túi tổng 7.2kg</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="0" t="inlineStr">
         <is>
           <t>Oplus</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="0" t="inlineStr">
         <is>
           <t>Nước giặt</t>
         </is>
       </c>
-      <c r="F41" t="n">
+      <c r="F41" s="0" t="n">
         <v>257592</v>
       </c>
-      <c r="G41" t="n">
+      <c r="G41" s="0" t="n">
         <v>585436</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H41" s="0" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I41" s="0" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J41" s="0" t="inlineStr">
         <is>
           <t>[COMBO] 4 túi Nước giặt xả 2in1 Oplus Hương nước hoa Pháp Sạch sâu mềm vải thơm lâu 4 túi tổng 7.2kg</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K41" s="0" t="inlineStr">
         <is>
           <t>2in1; nước giặt; oplus</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="L41" s="0" t="inlineStr">
         <is>
           <t>Oplus</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="M41" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/-COMBO-4-túi-Nước-giặt-xả-2in1-Oplus-Hương-nước-hoa-Pháp-Sạch-sâu-mềm-vải-thơm-lâu-4-túi-tổng-7.2kg-i.20523065.53011222501</t>
         </is>
       </c>
-      <c r="N41" t="b">
+      <c r="N41" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O41" s="14" t="n">
@@ -8372,62 +8372,62 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="b">
-        <v>1</v>
-      </c>
-      <c r="B42" t="n">
+      <c r="A42" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B42" s="0" t="n">
         <v>42723420756</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="0" t="inlineStr">
         <is>
           <t>Nước giặt Pano Elegant túi 1.8kg combo mua 1 được 3 hương nước hoa Pháp cổ điển giặt tay giặt máy sạch sâu vết bẩn</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="0" t="inlineStr">
         <is>
           <t>Nước giặt</t>
         </is>
       </c>
-      <c r="F42" t="n">
+      <c r="F42" s="0" t="n">
         <v>130693</v>
       </c>
-      <c r="G42" t="n">
+      <c r="G42" s="0" t="n">
         <v>251332</v>
       </c>
-      <c r="H42" t="n">
+      <c r="H42" s="0" t="n">
         <v>0.48</v>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I42" s="0" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J42" s="0" t="inlineStr">
         <is>
           <t>Nước giặt Pano Elegant túi 1.8kg combo mua 1 được 3 hương nước hoa Pháp cổ điển giặt tay giặt máy sạch sâu vết bẩn</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K42" s="0" t="inlineStr">
         <is>
           <t>1.8kg; elegant; nước giặt; pano</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L42" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="M42" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Nước-giặt-Pano-Elegant-túi-1.8kg-combo-mua-1-được-3-hương-nước-hoa-Pháp-cổ-điển-giặt-tay-giặt-máy-sạch-sâu-vết-bẩn-i.20523065.42723420756</t>
         </is>
       </c>
-      <c r="N42" t="b">
+      <c r="N42" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O42" s="14" t="n">
@@ -8435,62 +8435,62 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="b">
-        <v>1</v>
-      </c>
-      <c r="B43" t="n">
+      <c r="A43" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B43" s="0" t="n">
         <v>40373426171</v>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="0" t="inlineStr">
         <is>
           <t>Nước giặt Pano Active combo 2 túi 1.8kg tặng nước rửa chén 400g hương nước hoa Pháp sang trọng sạch sâu vết bẩn</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="0" t="inlineStr">
         <is>
           <t>Nước giặt</t>
         </is>
       </c>
-      <c r="F43" t="n">
+      <c r="F43" s="0" t="n">
         <v>120640</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G43" s="0" t="n">
         <v>251333</v>
       </c>
-      <c r="H43" t="n">
+      <c r="H43" s="0" t="n">
         <v>0.52</v>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" s="0" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J43" s="0" t="inlineStr">
         <is>
           <t>Nước giặt Pano Active combo 2 túi 1.8kg tặng nước rửa chén 400g hương nước hoa Pháp sang trọng sạch sâu vết bẩn</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K43" s="0" t="inlineStr">
         <is>
           <t>1.8kg; active; nước giặt; pano</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L43" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="M43" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Nước-giặt-Pano-Active-combo-2-túi-1.8kg-tặng-nước-rửa-chén-400g-hương-nước-hoa-Pháp-sang-trọng-sạch-sâu-vết-bẩn-i.20523065.40373426171</t>
         </is>
       </c>
-      <c r="N43" t="b">
+      <c r="N43" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O43" s="14" t="n">
@@ -8498,62 +8498,62 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="b">
-        <v>1</v>
-      </c>
-      <c r="B44" t="n">
+      <c r="A44" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B44" s="0" t="n">
         <v>26442724780</v>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="0" t="inlineStr">
         <is>
           <t>Combo 2 túi Nước giặt Pano Warmish 1.8kg hương táo dứa hoa nhài sạch sâu vết bẩn tặng nước rửa chén 200g</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="0" t="inlineStr">
         <is>
           <t>Nước giặt</t>
         </is>
       </c>
-      <c r="F44" t="n">
+      <c r="F44" s="0" t="n">
         <v>130693</v>
       </c>
-      <c r="G44" t="n">
+      <c r="G44" s="0" t="n">
         <v>242024</v>
       </c>
-      <c r="H44" t="n">
+      <c r="H44" s="0" t="n">
         <v>0.46</v>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I44" s="0" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J44" s="0" t="inlineStr">
         <is>
           <t>Combo 2 túi Nước giặt Pano Warmish 1.8kg hương táo dứa hoa nhài sạch sâu vết bẩn tặng nước rửa chén 200g</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K44" s="0" t="inlineStr">
         <is>
           <t>1.8kg; nước giặt; pano; warmish</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="L44" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="M44" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Combo-2-túi-Nước-giặt-Pano-Warmish-1.8kg-hương-táo-dứa-hoa-nhài-sạch-sâu-vết-bẩn-tặng-nước-rửa-chén-200g-i.20523065.26442724780</t>
         </is>
       </c>
-      <c r="N44" t="b">
+      <c r="N44" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O44" s="14" t="n">
@@ -8561,62 +8561,62 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="b">
-        <v>1</v>
-      </c>
-      <c r="B45" t="n">
+      <c r="A45" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B45" s="0" t="n">
         <v>43672853910</v>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="0" t="inlineStr">
         <is>
           <t>Combo 4 nước giặt Pano 1.8kg hương nước hoa Pháp giặt tay giặt máy sạch sâu vết bẩn an toàn cho da tay</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="0" t="inlineStr">
         <is>
           <t>Nước giặt</t>
         </is>
       </c>
-      <c r="F45" t="n">
+      <c r="F45" s="0" t="n">
         <v>239343</v>
       </c>
-      <c r="G45" t="n">
+      <c r="G45" s="0" t="n">
         <v>460275</v>
       </c>
-      <c r="H45" t="n">
+      <c r="H45" s="0" t="n">
         <v>0.48</v>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I45" s="0" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J45" s="0" t="inlineStr">
         <is>
           <t>Combo 4 nước giặt Pano 1.8kg hương nước hoa Pháp giặt tay giặt máy sạch sâu vết bẩn an toàn cho da tay</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K45" s="0" t="inlineStr">
         <is>
           <t>1.8kg; nước giặt; pano</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L45" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="M45" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Combo-4-nước-giặt-Pano-1.8kg-hương-nước-hoa-Pháp-giặt-tay-giặt-máy-sạch-sâu-vết-bẩn-an-toàn-cho-da-tay-i.20523065.43672853910</t>
         </is>
       </c>
-      <c r="N45" t="b">
+      <c r="N45" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O45" s="14" t="n">
@@ -8624,62 +8624,62 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="b">
-        <v>1</v>
-      </c>
-      <c r="B46" t="n">
+      <c r="A46" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B46" s="0" t="n">
         <v>27042559428</v>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="0" t="inlineStr">
         <is>
           <t>Thùng nước giặt Pano Active 6 túi hương nước hoa Pháp sang trọng giặt tay giặt máy sạch sâu an toàn da tay</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="0" t="inlineStr">
         <is>
           <t>Nước giặt</t>
         </is>
       </c>
-      <c r="F46" t="n">
+      <c r="F46" s="0" t="n">
         <v>681812</v>
       </c>
-      <c r="G46" t="n">
+      <c r="G46" s="0" t="n">
         <v>1311176</v>
       </c>
-      <c r="H46" t="n">
+      <c r="H46" s="0" t="n">
         <v>0.48</v>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I46" s="0" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J46" s="0" t="inlineStr">
         <is>
           <t>Thùng nước giặt Pano Active 6 túi hương nước hoa Pháp sang trọng giặt tay giặt máy sạch sâu an toàn da tay</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K46" s="0" t="inlineStr">
         <is>
           <t>active; nước giặt; pano</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="L46" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M46" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Thùng-nước-giặt-Pano-Active-6-túi-hương-nước-hoa-Pháp-sang-trọng-giặt-tay-giặt-máy-sạch-sâu-an-toàn-da-tay-i.20523065.27042559428</t>
         </is>
       </c>
-      <c r="N46" t="b">
+      <c r="N46" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O46" s="14" t="n">
@@ -8687,62 +8687,62 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="b">
-        <v>1</v>
-      </c>
-      <c r="B47" t="n">
+      <c r="A47" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B47" s="0" t="n">
         <v>29550492191</v>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="0" t="inlineStr">
         <is>
           <t>Nước giặt xả Oplus 2in1 can 3.5kg hương nước hoa Pháp không cần nước xả sạch sâu mềm vải lưu hương thơm lâu</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="0" t="inlineStr">
         <is>
           <t>Oplus</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="0" t="inlineStr">
         <is>
           <t>Nước giặt</t>
         </is>
       </c>
-      <c r="F47" t="n">
+      <c r="F47" s="0" t="n">
         <v>129390</v>
       </c>
-      <c r="G47" t="n">
+      <c r="G47" s="0" t="n">
         <v>208693</v>
       </c>
-      <c r="H47" t="n">
+      <c r="H47" s="0" t="n">
         <v>0.38</v>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I47" s="0" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J47" s="0" t="inlineStr">
         <is>
           <t>Nước giặt xả Oplus 2in1 can 3.5kg hương nước hoa Pháp không cần nước xả sạch sâu mềm vải lưu hương thơm lâu</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K47" s="0" t="inlineStr">
         <is>
           <t>2in1; can 3.5kg; nước giặt; oplus</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="L47" s="0" t="inlineStr">
         <is>
           <t>Oplus</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="M47" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Nước-giặt-xả-Oplus-2in1-can-3.5kg-hương-nước-hoa-Pháp-không-cần-nước-xả-sạch-sâu-mềm-vải-lưu-hương-thơm-lâu-i.20523065.29550492191</t>
         </is>
       </c>
-      <c r="N47" t="b">
+      <c r="N47" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O47" s="14" t="n">
@@ -8750,62 +8750,62 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="b">
-        <v>1</v>
-      </c>
-      <c r="B48" t="n">
+      <c r="A48" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B48" s="0" t="n">
         <v>42822813714</v>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="0" t="inlineStr">
         <is>
           <t>Thùng nước giặt Pano Fresh 6 túi hương táo hoa trắng giặt tay giặt máy sạch sâu vết bẩn an toàn da tay bán sỉ</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="0" t="inlineStr">
         <is>
           <t>Nước giặt</t>
         </is>
       </c>
-      <c r="F48" t="n">
+      <c r="F48" s="0" t="n">
         <v>681812</v>
       </c>
-      <c r="G48" t="n">
+      <c r="G48" s="0" t="n">
         <v>1311176</v>
       </c>
-      <c r="H48" t="n">
+      <c r="H48" s="0" t="n">
         <v>0.48</v>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I48" s="0" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J48" s="0" t="inlineStr">
         <is>
           <t>Thùng nước giặt Pano Fresh 6 túi hương táo hoa trắng giặt tay giặt máy sạch sâu vết bẩn an toàn da tay bán sỉ</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="K48" s="0" t="inlineStr">
         <is>
           <t>fresh; nước giặt; pano</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="L48" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="M48" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Thùng-nước-giặt-Pano-Fresh-6-túi-hương-táo-hoa-trắng-giặt-tay-giặt-máy-sạch-sâu-vết-bẩn-an-toàn-da-tay-bán-sỉ-i.20523065.42822813714</t>
         </is>
       </c>
-      <c r="N48" t="b">
+      <c r="N48" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O48" s="14" t="n">
@@ -8813,62 +8813,62 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="b">
-        <v>1</v>
-      </c>
-      <c r="B49" t="n">
+      <c r="A49" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B49" s="0" t="n">
         <v>29842549801</v>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="0" t="inlineStr">
         <is>
           <t>Thùng nước giặt Pano Warmish6 túi hương táo dứa hoa nhài giặt tay giặt máy sạch sâu an toàn da tay bán sỉ</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="0" t="inlineStr">
         <is>
           <t>Nước giặt</t>
         </is>
       </c>
-      <c r="F49" t="n">
+      <c r="F49" s="0" t="n">
         <v>552653</v>
       </c>
-      <c r="G49" t="n">
+      <c r="G49" s="0" t="n">
         <v>1151360</v>
       </c>
-      <c r="H49" t="n">
+      <c r="H49" s="0" t="n">
         <v>0.52</v>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I49" s="0" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J49" s="0" t="inlineStr">
         <is>
           <t>Thùng nước giặt Pano Warmish6 túi hương táo dứa hoa nhài giặt tay giặt máy sạch sâu an toàn da tay bán sỉ</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K49" s="0" t="inlineStr">
         <is>
           <t>nước giặt; pano; warmish</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="L49" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="M49" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Thùng-nước-giặt-Pano-Warmish6-túi-hương-táo-dứa-hoa-nhài-giặt-tay-giặt-máy-sạch-sâu-an-toàn-da-tay-bán-sỉ-i.20523065.29842549801</t>
         </is>
       </c>
-      <c r="N49" t="b">
+      <c r="N49" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O49" s="14" t="n">
@@ -8876,62 +8876,62 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="b">
-        <v>1</v>
-      </c>
-      <c r="B50" t="n">
+      <c r="A50" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B50" s="0" t="n">
         <v>26042584534</v>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="0" t="inlineStr">
         <is>
           <t>Thùng nước giặt Pano Elegant 6 túi hương nước hoa Pháp cổ điển giặt tay giặt máy sạch sâu an toàn da tay</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="0" t="inlineStr">
         <is>
           <t>Nước giặt</t>
         </is>
       </c>
-      <c r="F50" t="n">
+      <c r="F50" s="0" t="n">
         <v>555939</v>
       </c>
-      <c r="G50" t="n">
+      <c r="G50" s="0" t="n">
         <v>1292881</v>
       </c>
-      <c r="H50" t="n">
+      <c r="H50" s="0" t="n">
         <v>0.57</v>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I50" s="0" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J50" s="0" t="inlineStr">
         <is>
           <t>Thùng nước giặt Pano Elegant 6 túi hương nước hoa Pháp cổ điển giặt tay giặt máy sạch sâu an toàn da tay</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="K50" s="0" t="inlineStr">
         <is>
           <t>elegant; nước giặt; pano</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="L50" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="M50" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Thùng-nước-giặt-Pano-Elegant-6-túi-hương-nước-hoa-Pháp-cổ-điển-giặt-tay-giặt-máy-sạch-sâu-an-toàn-da-tay-i.20523065.26042584534</t>
         </is>
       </c>
-      <c r="N50" t="b">
+      <c r="N50" s="0" t="b">
         <v>1</v>
       </c>
       <c r="O50" s="14" t="n">
@@ -8939,195 +8939,195 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="b">
-        <v>1</v>
-      </c>
-      <c r="B51" t="n">
+      <c r="A51" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B51" s="0" t="n">
         <v>19819336767</v>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="0" t="inlineStr">
         <is>
           <t>Nước tẩy toilet đậm đặc Pano Hương trái cây Tẩy cặn vôi ố vàng khử mùi hôi Chai 960g</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="0" t="inlineStr">
         <is>
           <t>Tẩy Toilet</t>
         </is>
       </c>
-      <c r="F51" t="n">
+      <c r="F51" s="0" t="n">
         <v>30000</v>
       </c>
-      <c r="G51" t="n">
+      <c r="G51" s="0" t="n">
         <v>30000</v>
       </c>
-      <c r="H51" t="n">
+      <c r="H51" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I51" s="0" t="inlineStr">
         <is>
           <t>OUT_OF_STOCK</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J51" s="0" t="inlineStr">
         <is>
           <t>Nước tẩy toilet đậm đặc Pano Hương trái cây Tẩy cặn vôi ố vàng khử mùi hôi Chai 960g</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K51" s="0" t="inlineStr">
         <is>
           <t>pano; tẩy toilet</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="L51" s="0" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="M51" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Nước-tẩy-toilet-đậm-đặc-Pano-Hương-trái-cây-Tẩy-cặn-vôi-ố-vàng-khử-mùi-hôi-Chai-960g-i.20523065.19819336767</t>
         </is>
       </c>
-      <c r="N51" t="b">
+      <c r="N51" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="O51" s="0" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="b">
-        <v>1</v>
-      </c>
-      <c r="B52" t="n">
+      <c r="A52" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B52" s="0" t="n">
         <v>20825187721</v>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="0" t="inlineStr">
         <is>
           <t>Nước tẩy quần áo màu Oxy Active ZeO Hương cam chanh oải hương Tẩy vết bẩn giữ màu không phai Chai 400ml</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="0" t="inlineStr">
         <is>
           <t>Nước tẩy quần áo màu</t>
         </is>
       </c>
-      <c r="F52" t="n">
+      <c r="F52" s="0" t="n">
         <v>39000</v>
       </c>
-      <c r="G52" t="n">
+      <c r="G52" s="0" t="n">
         <v>39000</v>
       </c>
-      <c r="H52" t="n">
+      <c r="H52" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I52" s="0" t="inlineStr">
         <is>
           <t>OUT_OF_STOCK</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J52" s="0" t="inlineStr">
         <is>
           <t>Nước tẩy quần áo màu Oxy Active ZeO Hương cam chanh oải hương Tẩy vết bẩn giữ màu không phai Chai 400ml</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K52" s="0" t="inlineStr">
         <is>
           <t>active; cam chanh; nước tẩy quần áo màu; zeo</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="L52" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="M52" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Nước-tẩy-quần-áo-màu-Oxy-Active-ZeO-Hương-cam-chanh-oải-hương-Tẩy-vết-bẩn-giữ-màu-không-phai-Chai-400ml-i.20523065.20825187721</t>
         </is>
       </c>
-      <c r="N52" t="b">
+      <c r="N52" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="O52" s="0" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="b">
-        <v>1</v>
-      </c>
-      <c r="B53" t="n">
+      <c r="A53" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="B53" s="0" t="n">
         <v>18983291625</v>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="0" t="inlineStr">
         <is>
           <t>Bộ 4 Tinh dầu thơm phòng 4in1 ZeO Hương SPA bưởi biển Midnight Khử mùi thư giãn 4 chai kèm kẹp treo</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="0" t="inlineStr">
         <is>
           <t>Tinh dầu &amp; Nước hoa</t>
         </is>
       </c>
-      <c r="F53" t="n">
+      <c r="F53" s="0" t="n">
         <v>233367</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G53" s="0" t="n">
         <v>288107</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H53" s="0" t="n">
         <v>0.19</v>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I53" s="0" t="inlineStr">
         <is>
           <t>OUT_OF_STOCK</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J53" s="0" t="inlineStr">
         <is>
           <t>Bộ 4 Tinh dầu thơm phòng 4in1 ZeO Hương SPA bưởi biển Midnight Khử mùi thư giãn 4 chai kèm kẹp treo</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K53" s="0" t="inlineStr">
         <is>
           <t>tinh dầu &amp; nước hoa; zeo</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="L53" s="0" t="inlineStr">
         <is>
           <t>ZeO</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="M53" s="0" t="inlineStr">
         <is>
           <t>https://shopee.vn/Bộ-4-Tinh-dầu-thơm-phòng-4in1-ZeO-Hương-SPA-bưởi-biển-Midnight-Khử-mùi-thư-giãn-4-chai-kèm-kẹp-treo-i.20523065.18983291625</t>
         </is>
       </c>
-      <c r="N53" t="b">
+      <c r="N53" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="O53" s="0" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
@@ -9160,61 +9160,61 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>item_id</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="G1" s="15" t="inlineStr">
-        <is>
-          <t>link_web</t>
-        </is>
-      </c>
-      <c r="H1" s="15" t="inlineStr">
+      <c r="G1" s="16" t="inlineStr">
+        <is>
+          <t>link_lazada</t>
+        </is>
+      </c>
+      <c r="H1" s="16" t="inlineStr">
         <is>
           <t>in_stock</t>
         </is>
       </c>
-      <c r="I1" s="15" t="inlineStr">
+      <c r="I1" s="16" t="inlineStr">
         <is>
           <t>keywords</t>
         </is>
       </c>
-      <c r="J1" s="15" t="inlineStr">
+      <c r="J1" s="16" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>(Thêm data vào đây khi có link website zeo.com.vn)</t>
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>(Thêm data vào đây khi có link Lazada)</t>
         </is>
       </c>
     </row>
@@ -9229,77 +9229,990 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" style="12" min="1" max="1"/>
-    <col width="22" customWidth="1" style="12" min="2" max="2"/>
-    <col width="55" customWidth="1" style="12" min="3" max="3"/>
-    <col width="22" customWidth="1" style="12" min="4" max="4"/>
-    <col width="22" customWidth="1" style="12" min="5" max="5"/>
-    <col width="22" customWidth="1" style="12" min="6" max="6"/>
+    <col width="20" customWidth="1" style="12" min="1" max="1"/>
+    <col width="20" customWidth="1" style="12" min="2" max="2"/>
+    <col width="60" customWidth="1" style="12" min="3" max="3"/>
+    <col width="20" customWidth="1" style="12" min="4" max="4"/>
+    <col width="20" customWidth="1" style="12" min="5" max="5"/>
+    <col width="20" customWidth="1" style="12" min="6" max="6"/>
     <col width="80" customWidth="1" style="12" min="7" max="7"/>
-    <col width="22" customWidth="1" style="12" min="8" max="8"/>
-    <col width="22" customWidth="1" style="12" min="9" max="9"/>
-    <col width="22" customWidth="1" style="12" min="10" max="10"/>
+    <col width="20" customWidth="1" style="12" min="8" max="8"/>
+    <col width="40" customWidth="1" style="12" min="9" max="9"/>
+    <col width="20" customWidth="1" style="12" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="B1" s="16" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>item_id</t>
         </is>
       </c>
-      <c r="C1" s="16" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="16" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="E1" s="16" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="F1" s="16" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="G1" s="16" t="inlineStr">
-        <is>
-          <t>link_lazada</t>
-        </is>
-      </c>
-      <c r="H1" s="16" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
+        <is>
+          <t>link_web</t>
+        </is>
+      </c>
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>in_stock</t>
         </is>
       </c>
-      <c r="I1" s="16" t="inlineStr">
+      <c r="I1" s="15" t="inlineStr">
         <is>
           <t>keywords</t>
         </is>
       </c>
-      <c r="J1" s="16" t="inlineStr">
+      <c r="J1" s="15" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>(Thêm data vào đây khi có link Lazada)</t>
+      <c r="A2" t="b">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>13582347</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Bột giặt ZeO Nước Hoa Tím túi 4.5Kg</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ZeO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Bột giặt</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://zeo.vn/bot-giat-zeo-khu-mui-manh-me</t>
+        </is>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>zeo; bột giặt; nước hoa; tím</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="b">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>13582869</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Nước giặt PANO Khử Mùi Hương Đam Mê Tím Can 3.8kg</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PANO</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Nước giặt</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>170000</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://zeo.vn/nuoc-giat-pano-khu-mui-huong-dam-me-tim-3800</t>
+        </is>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>pano; nước giặt; tím; khử mùi</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>13585248</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Nước Giặt OPLUS 2in1 Khử Mùi Mềm Vải Tím Can 1kg</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Oplus</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Nước giặt</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>47000</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://zeo.vn/nuoc-giat-oplus-khu-mui-1kg-tim</t>
+        </is>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>oplus; nước giặt; tím; 2in1; khử mùi</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="b">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>13632222</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Nước tẩy Javel - ZeO 1 lít</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ZeO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Nước tẩy</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://zeo.vn/nuoc-tay-javel-zeo-1lit</t>
+        </is>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>zeo; nước tẩy; javel</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>14571256</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bột Giặt OPLUS Tiết Kiệm Nước Túi 2kg</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Oplus</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Bột giặt</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>62000</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://zeo.vn/bot-giat-oplus-tiet-kiem-nuoc-2kg</t>
+        </is>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>oplus; bột giặt; tiết kiệm nước</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="b">
+        <v>1</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>22085531</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Nước giặt Pano Khử Mùi Can Tím 3.8Kg</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PANO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Nước giặt</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>124000</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://zeo.vn/nuoc-giat-pano-khu-mui-can-tim-3800g</t>
+        </is>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>pano; nước giặt; tím; khử mùi</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="b">
+        <v>1</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>27456489</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Nước giặt xả ZeO 3in1 Polymer Bạc Diệt Khuẩn Túi 2,2kg</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ZeO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Nước giặt xả</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>111000</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://zeo.vn/nuoc-giat-xa-zeo-3in1-tui-2-2kg</t>
+        </is>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>zeo; nước giặt xả; 3in1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="b">
+        <v>1</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>38863750</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Oplus sạch nhanh can 1,5kg</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Oplus</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Nước rửa chén</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>37000</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://zeo.vn/nuoc-rua-chen-oplus-sach-nhanh-1-5-kg</t>
+        </is>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>oplus; nước rửa chén</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>83638937</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Nước giặt Oplus Xanh Ngàn Hoa Dịu Nhẹ Chai 1kg</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Oplus</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Nước giặt</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>47000</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://zeo.vn/nuoc-giat-oplus-xanh</t>
+        </is>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>oplus; nước giặt; xanh</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="b">
+        <v>1</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>84103652</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Nước giặt Zeo BiO Enzyme sạch siêu nhanh 3 phút can 2Kg</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ZeO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Nước giặt</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>89000</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://zeo.vn/nuoc-giat-zeo-bio-enzyme-sach-sieu-nhanh-3-phut-2-kg</t>
+        </is>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>zeo; nước giặt; enzyme; bio enzyme</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="b">
+        <v>1</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>84103834</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Nước giặt Zeo BiO Enzyme sạch siêu nhanh 3 phút can 9 Kg</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ZeO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Nước giặt</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>237000</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://zeo.vn/nuoc-giat-zeo-bio-enzyme-sach-sieu-nhanh-3-phut-9-kg</t>
+        </is>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>zeo; nước giặt; enzyme; bio enzyme</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="b">
+        <v>1</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>84117293</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Oplus 2in1 lưu hương kép hương nước hoa Pháp 1,8 Kg</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Oplus</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Nước giặt xả</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>67000</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://zeo.vn/nuoc-giat-xa-oplus-2in1-luu-huong-kep-bao-tim-1-8-kg</t>
+        </is>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>oplus; nước giặt xả; nước hoa; 2in1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="b">
+        <v>1</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>84119895</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Nước lau sàn Oplus hương sả chanh chai 1kg</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Oplus</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Nước lau sàn</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>27000</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://zeo.vn/nuoc-lau-san-oplus-huong-sa-chanh-1-kg</t>
+        </is>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>oplus; nước lau sàn; chanh; sả chanh</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="b">
+        <v>1</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>84452351</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Nước giặt Oplus Xanh Ngàn Hoa Dịu Nhẹ Can 3.5kg</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Oplus</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Nước giặt</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>137000</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://zeo.vn/nuoc-giat-oplus-xanh-ngan-hoa-diu-nhe-can-3-5kg</t>
+        </is>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>oplus; nước giặt; xanh</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="b">
+        <v>1</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>84452714</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Nước rửa chén ZEO enzyme hương chanh chai 1.5kg</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ZeO</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Nước rửa chén</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>37000</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://zeo.vn/nuoc-rua-chen-zeo-enzim-huong-chanh-chai-1500g</t>
+        </is>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>zeo; nước rửa chén; chanh; enzyme</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="b">
+        <v>1</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>84453004</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Pano Vitamin E Túi 3.5kg</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PANO</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Nước rửa chén</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>59000</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://zeo.vn/nuoc-rua-chen-pano-vitamin-e-tui-3500</t>
+        </is>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>pano; nước rửa chén; vitamin e</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="b">
+        <v>1</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>84479406</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Oplus 2in1 hương đỏ quyến rũ chai 3,5kg</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Oplus</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Nước giặt xả</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>146000</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://zeo.vn/nuoc-giat-xa-oplus-2in1-huong-do-quyen-ru-chai-3500</t>
+        </is>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>oplus; nước giặt xả; 2in1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="b">
+        <v>1</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>84511753</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Nước giặt Pano Khử Mùi Can Xanh 3.8Kg</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PANO</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Nước giặt</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>124000</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://zeo.vn/nuoc-giat-pano-khu-mui-can-xanh-3-8kg</t>
+        </is>
+      </c>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>pano; nước giặt; xanh; khử mùi</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="b">
+        <v>1</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>84560089</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Nước Giặt OPLUS 2in1 Khử Mùi Mềm Vải Tím Can 3.5kg</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Oplus</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Nước giặt</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>139000</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://zeo.vn/nuoc-giat-oplus-2in1-khu-mui-mem-vai-tim-can-3500</t>
+        </is>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>oplus; nước giặt; tím; 2in1; khử mùi</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="b">
+        <v>1</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>84560744</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Oplus 2in1 lưu hương kép hương hoa Peony 1,8 Kg</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Oplus</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Nước giặt xả</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>92000</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://zeo.vn/nuoc-giat-xa-oplus-2in1-luu-huong-kep-huong-hoa-peony-1-8-kg</t>
+        </is>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>oplus; nước giặt xả; peony; 2in1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
